--- a/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13632,7 +13632,7 @@
         <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>0.676435</v>
+        <v>0.6584719999999999</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.6802049999999999</v>
+        <v>0.541685</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>0</v>
       </c>
       <c r="G309" t="n">
-        <v>0.315599</v>
+        <v>0.24487</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.404673</v>
+        <v>0.491733</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13801,10 +13801,10 @@
         <v>0.076319</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0.399086</v>
+        <v>0.557212</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.290188</v>
+        <v>0.168168</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>0.783793</v>
+        <v>0.860795</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>0.525638</v>
+        <v>0.676076</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.292267</v>
+        <v>0.277961</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.192137</v>
+        <v>0.287797</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.267532</v>
+        <v>0.305802</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.525147</v>
+        <v>0.596508</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.209225</v>
+        <v>0.218892</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.6329</v>
+        <v>0.708116</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.416893</v>
+        <v>0.469409</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14274,10 +14274,10 @@
         <v>0.004881</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.546932</v>
+        <v>0.433868</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.205813</v>
+        <v>0.272031</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.138229</v>
+        <v>0.161514</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.253948</v>
+        <v>0.252109</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.370499</v>
+        <v>0.45684</v>
       </c>
       <c r="H326" t="n">
         <v>1</v>
@@ -14492,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>0.7634069999999999</v>
+        <v>0.767877</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14532,10 +14532,10 @@
         <v>2e-06</v>
       </c>
       <c r="F328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.448131</v>
+        <v>0.525201</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>0.703975</v>
+        <v>0.72338</v>
       </c>
       <c r="H329" t="n">
         <v>1</v>
@@ -14621,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0.768961</v>
+        <v>0.797078</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.736731</v>
+        <v>0.785208</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.212308</v>
+        <v>0.156473</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>0</v>
       </c>
       <c r="G333" t="n">
-        <v>0.15866</v>
+        <v>0.221655</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.098222</v>
+        <v>0.178167</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0.001309</v>
       </c>
       <c r="F335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G335" t="n">
-        <v>0.473884</v>
+        <v>0.599377</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>5.2e-05</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0.482234</v>
+        <v>0.778232</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14919,10 +14919,10 @@
         <v>0.024552</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.542604</v>
+        <v>0.499733</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.238505</v>
+        <v>0.305816</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.346868</v>
+        <v>0.345413</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.027054</v>
       </c>
       <c r="F340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>0.470721</v>
+        <v>0.626941</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.220078</v>
+        <v>0.266981</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.176339</v>
+        <v>0.222938</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.234322</v>
+        <v>0.232685</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>0.53939</v>
+        <v>0.561317</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0.730965</v>
+        <v>0.889537</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.244988</v>
+        <v>0.153015</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15349,10 +15349,10 @@
         <v>0</v>
       </c>
       <c r="F347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>0.496462</v>
+        <v>0.615362</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.206886</v>
+        <v>0.192291</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.257194</v>
+        <v>0.247085</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0.255583</v>
+        <v>0.275149</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.179286</v>
+        <v>0.148225</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.332929</v>
+        <v>0.302368</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.490234</v>
+        <v>0.423625</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>0.916708</v>
+        <v>0.946971</v>
       </c>
       <c r="H354" t="n">
         <v>1</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.277493</v>
+        <v>0.13621</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0.624949</v>
+        <v>0.663833</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0.6830270000000001</v>
+        <v>0.560092</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.69014</v>
+        <v>0.532316</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0.519183</v>
+        <v>0.530041</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.8092279999999999</v>
+        <v>0.908218</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.542777</v>
+        <v>0.569497</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0.456187</v>
+        <v>0.499243</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.297162</v>
+        <v>0.343489</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0.456185</v>
+        <v>0.361214</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.352193</v>
+        <v>0.458051</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.204396</v>
+        <v>0.264794</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.295543</v>
+        <v>0.396215</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.256929</v>
+        <v>0.2699</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.147725</v>
+        <v>0.163702</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.239376</v>
+        <v>0.161599</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.376506</v>
+        <v>0.287207</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>1</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6901350000000001</v>
+        <v>0.711286</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.305103</v>
+        <v>0.241141</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.322605</v>
+        <v>0.257401</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.313219</v>
+        <v>0.300714</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>0.635124</v>
+        <v>0.69306</v>
       </c>
       <c r="H376" t="n">
         <v>1</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.385091</v>
+        <v>0.298073</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.264115</v>
+        <v>0.191932</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.464906</v>
+        <v>0.332588</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.345359</v>
+        <v>0.28844</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.317317</v>
+        <v>0.255392</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.534313</v>
+        <v>0.590097</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.363616</v>
+        <v>0.318479</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.314949</v>
+        <v>0.253918</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.464351</v>
+        <v>0.411959</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.284061</v>
+        <v>0.309972</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17069,10 +17069,10 @@
         <v>0</v>
       </c>
       <c r="F387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G387" t="n">
-        <v>0.421951</v>
+        <v>0.515002</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.406029</v>
+        <v>0.270792</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.466737</v>
+        <v>0.49956</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.434804</v>
+        <v>0.351693</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>0.597144</v>
+        <v>0.556032</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.73232</v>
+        <v>0.879611</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="G393" t="n">
-        <v>0.374456</v>
+        <v>0.333919</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.295261</v>
+        <v>0.264804</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>0</v>
       </c>
       <c r="G395" t="n">
-        <v>0.477474</v>
+        <v>0.492208</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.368529</v>
+        <v>0.16929</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.345634</v>
+        <v>0.28171</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.40837</v>
+        <v>0.386321</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.275049</v>
+        <v>0.278039</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.280428</v>
+        <v>0.193298</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.263797</v>
+        <v>0.21521</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0.73384</v>
+        <v>0.81973</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>0</v>
       </c>
       <c r="G403" t="n">
-        <v>0.276363</v>
+        <v>0.186471</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.173081</v>
+        <v>0.198228</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.330076</v>
+        <v>0.302419</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.261954</v>
+        <v>0.176205</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.7622100000000001</v>
+        <v>0.929414</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="G408" t="n">
-        <v>0.135592</v>
+        <v>0.129455</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.383671</v>
+        <v>0.277432</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.296039</v>
+        <v>0.258673</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.341976</v>
+        <v>0.230859</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.85498</v>
+        <v>0.942248</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>1</v>
       </c>
       <c r="G413" t="n">
-        <v>0.62224</v>
+        <v>0.544019</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="G414" t="n">
-        <v>0.350812</v>
+        <v>0.325232</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -18276,7 +18276,7 @@
         <v>0</v>
       </c>
       <c r="G415" t="n">
-        <v>0.273175</v>
+        <v>0.181121</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -18319,7 +18319,7 @@
         <v>0</v>
       </c>
       <c r="G416" t="n">
-        <v>0.309337</v>
+        <v>0.23962</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -18362,7 +18362,7 @@
         <v>0</v>
       </c>
       <c r="G417" t="n">
-        <v>0.297221</v>
+        <v>0.265752</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -18405,7 +18405,7 @@
         <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>0.2989</v>
+        <v>0.246821</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -18448,7 +18448,7 @@
         <v>1</v>
       </c>
       <c r="G419" t="n">
-        <v>0.593137</v>
+        <v>0.682958</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="G420" t="n">
-        <v>0.337324</v>
+        <v>0.336638</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -18534,7 +18534,7 @@
         <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>0.376864</v>
+        <v>0.366543</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -18577,7 +18577,7 @@
         <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>0.318086</v>
+        <v>0.217807</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -18617,10 +18617,10 @@
         <v>3e-05</v>
       </c>
       <c r="F423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>0.435199</v>
+        <v>0.513154</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="G424" t="n">
-        <v>0.197458</v>
+        <v>0.182836</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -18706,7 +18706,7 @@
         <v>0</v>
       </c>
       <c r="G425" t="n">
-        <v>0.486616</v>
+        <v>0.31437</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -18749,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0.653567</v>
+        <v>0.674439</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -18792,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="G427" t="n">
-        <v>0.593428</v>
+        <v>0.591813</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -18835,7 +18835,7 @@
         <v>0</v>
       </c>
       <c r="G428" t="n">
-        <v>0.279509</v>
+        <v>0.270803</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="G429" t="n">
-        <v>0.387006</v>
+        <v>0.324191</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -18921,7 +18921,7 @@
         <v>1</v>
       </c>
       <c r="G430" t="n">
-        <v>0.530721</v>
+        <v>0.519607</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -18961,10 +18961,10 @@
         <v>0</v>
       </c>
       <c r="F431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G431" t="n">
-        <v>0.25654</v>
+        <v>0.5265919999999999</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
         <v>0</v>
       </c>
       <c r="G432" t="n">
-        <v>0.266516</v>
+        <v>0.195478</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -19047,10 +19047,10 @@
         <v>8e-06</v>
       </c>
       <c r="F433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G433" t="n">
-        <v>0.558836</v>
+        <v>0.419821</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -19093,7 +19093,7 @@
         <v>1</v>
       </c>
       <c r="G434" t="n">
-        <v>0.5556990000000001</v>
+        <v>0.616165</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -19136,7 +19136,7 @@
         <v>0</v>
       </c>
       <c r="G435" t="n">
-        <v>0.280829</v>
+        <v>0.292134</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -19179,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="G436" t="n">
-        <v>0.22955</v>
+        <v>0.170253</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -19222,7 +19222,7 @@
         <v>0</v>
       </c>
       <c r="G437" t="n">
-        <v>0.292812</v>
+        <v>0.227541</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -19265,7 +19265,7 @@
         <v>0</v>
       </c>
       <c r="G438" t="n">
-        <v>0.424392</v>
+        <v>0.353991</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -19305,10 +19305,10 @@
         <v>0.005117</v>
       </c>
       <c r="F439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G439" t="n">
-        <v>0.558648</v>
+        <v>0.420096</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -19348,10 +19348,10 @@
         <v>0.034541</v>
       </c>
       <c r="F440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G440" t="n">
-        <v>0.517995</v>
+        <v>0.450401</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -19391,10 +19391,10 @@
         <v>0.003569</v>
       </c>
       <c r="F441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G441" t="n">
-        <v>0.501868</v>
+        <v>0.425995</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -19437,7 +19437,7 @@
         <v>0</v>
       </c>
       <c r="G442" t="n">
-        <v>0.441392</v>
+        <v>0.38203</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>0</v>
       </c>
       <c r="G443" t="n">
-        <v>0.335693</v>
+        <v>0.31748</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -19523,7 +19523,7 @@
         <v>0</v>
       </c>
       <c r="G444" t="n">
-        <v>0.210627</v>
+        <v>0.347554</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -19566,7 +19566,7 @@
         <v>0</v>
       </c>
       <c r="G445" t="n">
-        <v>0.283084</v>
+        <v>0.196503</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -19609,7 +19609,7 @@
         <v>0</v>
       </c>
       <c r="G446" t="n">
-        <v>0.236379</v>
+        <v>0.181031</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
         <v>1</v>
       </c>
       <c r="G447" t="n">
-        <v>0.642068</v>
+        <v>0.6096510000000001</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -19695,7 +19695,7 @@
         <v>0</v>
       </c>
       <c r="G448" t="n">
-        <v>0.172464</v>
+        <v>0.153227</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
         <v>0</v>
       </c>
       <c r="G449" t="n">
-        <v>0.341555</v>
+        <v>0.427081</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -19781,7 +19781,7 @@
         <v>0</v>
       </c>
       <c r="G450" t="n">
-        <v>0.367253</v>
+        <v>0.350434</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -19821,10 +19821,10 @@
         <v>0.002123</v>
       </c>
       <c r="F451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G451" t="n">
-        <v>0.547115</v>
+        <v>0.36578</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -19867,7 +19867,7 @@
         <v>0</v>
       </c>
       <c r="G452" t="n">
-        <v>0.311871</v>
+        <v>0.282258</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
         <v>0</v>
       </c>
       <c r="G453" t="n">
-        <v>0.321355</v>
+        <v>0.272707</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -19950,10 +19950,10 @@
         <v>0.050069</v>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G454" t="n">
-        <v>0.5346340000000001</v>
+        <v>0.473148</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -19996,7 +19996,7 @@
         <v>0</v>
       </c>
       <c r="G455" t="n">
-        <v>0.265798</v>
+        <v>0.147998</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -20036,10 +20036,10 @@
         <v>1.6e-05</v>
       </c>
       <c r="F456" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G456" t="n">
-        <v>0.537787</v>
+        <v>0.475308</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -20082,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="G457" t="n">
-        <v>0.242423</v>
+        <v>0.211308</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         <v>0</v>
       </c>
       <c r="G458" t="n">
-        <v>0.294719</v>
+        <v>0.229643</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -20168,7 +20168,7 @@
         <v>0</v>
       </c>
       <c r="G459" t="n">
-        <v>0.341766</v>
+        <v>0.264764</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -20211,7 +20211,7 @@
         <v>0</v>
       </c>
       <c r="G460" t="n">
-        <v>0.345004</v>
+        <v>0.232539</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -20254,7 +20254,7 @@
         <v>0</v>
       </c>
       <c r="G461" t="n">
-        <v>0.349614</v>
+        <v>0.240249</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -20294,10 +20294,10 @@
         <v>0.015801</v>
       </c>
       <c r="F462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G462" t="n">
-        <v>0.482155</v>
+        <v>0.503023</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -20340,7 +20340,7 @@
         <v>0</v>
       </c>
       <c r="G463" t="n">
-        <v>0.477631</v>
+        <v>0.492111</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -20383,7 +20383,7 @@
         <v>0</v>
       </c>
       <c r="G464" t="n">
-        <v>0.27872</v>
+        <v>0.204846</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -20426,7 +20426,7 @@
         <v>0</v>
       </c>
       <c r="G465" t="n">
-        <v>0.381301</v>
+        <v>0.354119</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -20469,7 +20469,7 @@
         <v>0</v>
       </c>
       <c r="G466" t="n">
-        <v>0.38053</v>
+        <v>0.320942</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -20512,7 +20512,7 @@
         <v>1</v>
       </c>
       <c r="G467" t="n">
-        <v>0.546964</v>
+        <v>0.563399</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -20555,7 +20555,7 @@
         <v>1</v>
       </c>
       <c r="G468" t="n">
-        <v>0.594301</v>
+        <v>0.501835</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -20598,7 +20598,7 @@
         <v>0</v>
       </c>
       <c r="G469" t="n">
-        <v>0.401755</v>
+        <v>0.378574</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
